--- a/data/excel/export_result.xlsx
+++ b/data/excel/export_result.xlsx
@@ -273,7 +273,7 @@
     </row>
     <row r="2" customHeight="true" ht="14.0">
       <c r="A2" s="5" t="n">
-        <v>317.0</v>
+        <v>331.0</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
@@ -328,7 +328,7 @@
     </row>
     <row r="3" customHeight="true" ht="14.0">
       <c r="A3" s="5" t="n">
-        <v>318.0</v>
+        <v>332.0</v>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
